--- a/templates/deliverable/example/03_컬럼정의서.xlsx
+++ b/templates/deliverable/example/03_컬럼정의서.xlsx
@@ -12,48 +12,66 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>컬럼 정의서</t>
   </si>
   <si>
+    <t>영문 테이블명</t>
+  </si>
+  <si>
+    <t>한글 컬럼명</t>
+  </si>
+  <si>
+    <t>영문 컬럼명</t>
+  </si>
+  <si>
+    <t>컬럼 설명</t>
+  </si>
+  <si>
+    <t>연관 엔터티명</t>
+  </si>
+  <si>
+    <t>연관 속성명</t>
+  </si>
+  <si>
+    <t>데이터 타입</t>
+  </si>
+  <si>
+    <t>데이터 길이</t>
+  </si>
+  <si>
+    <t>Not Null 여부</t>
+  </si>
+  <si>
+    <t>PK정보</t>
+  </si>
+  <si>
+    <t>AK정보</t>
+  </si>
+  <si>
+    <t>FK정보</t>
+  </si>
+  <si>
+    <t>제약조건</t>
+  </si>
+  <si>
+    <t>개인정보 여부</t>
+  </si>
+  <si>
+    <t>암호화 여부</t>
+  </si>
+  <si>
+    <t>공개/비공개 여부</t>
+  </si>
+  <si>
     <t>순번</t>
   </si>
   <si>
     <t>스키마명</t>
   </si>
   <si>
-    <t>테이블명</t>
-  </si>
-  <si>
-    <t>컬럼명(영문)</t>
-  </si>
-  <si>
-    <t>컬럼명(한글)</t>
-  </si>
-  <si>
-    <t>연관엔터티명</t>
-  </si>
-  <si>
-    <t>연관속성명</t>
-  </si>
-  <si>
-    <t>Not Null</t>
-  </si>
-  <si>
-    <t>데이터타입</t>
-  </si>
-  <si>
-    <t>데이터길이</t>
-  </si>
-  <si>
     <t>기본값</t>
-  </si>
-  <si>
-    <t>PK정보</t>
-  </si>
-  <si>
-    <t>컬럼설명</t>
   </si>
   <si>
     <t>담당부서</t>
@@ -89,12 +107,12 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="11.0"/>
+      <sz val="14.0"/>
       <b val="true"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="14.0"/>
+      <sz val="11.0"/>
       <b val="true"/>
     </font>
   </fonts>
@@ -148,8 +166,8 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true"/>
   </cellXfs>
 </styleSheet>
@@ -157,28 +175,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:Y3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="8.0" customWidth="true"/>
-    <col min="2" max="2" width="12.0" customWidth="true"/>
-    <col min="3" max="3" width="12.0" customWidth="true"/>
-    <col min="4" max="4" width="18.0" customWidth="true"/>
+    <col min="1" max="1" width="18.0" customWidth="true"/>
+    <col min="2" max="2" width="16.0" customWidth="true"/>
+    <col min="3" max="3" width="16.0" customWidth="true"/>
+    <col min="4" max="4" width="14.0" customWidth="true"/>
     <col min="5" max="5" width="18.0" customWidth="true"/>
     <col min="6" max="6" width="16.0" customWidth="true"/>
-    <col min="7" max="7" width="14.0" customWidth="true"/>
-    <col min="8" max="8" width="20.0" customWidth="true"/>
-    <col min="9" max="9" width="14.0" customWidth="true"/>
-    <col min="10" max="10" width="14.0" customWidth="true"/>
-    <col min="11" max="11" width="10.0" customWidth="true"/>
+    <col min="7" max="7" width="16.0" customWidth="true"/>
+    <col min="8" max="8" width="16.0" customWidth="true"/>
+    <col min="9" max="9" width="26.0" customWidth="true"/>
+    <col min="10" max="10" width="12.0" customWidth="true"/>
+    <col min="11" max="11" width="12.0" customWidth="true"/>
     <col min="12" max="12" width="12.0" customWidth="true"/>
     <col min="13" max="13" width="12.0" customWidth="true"/>
-    <col min="14" max="14" width="12.0" customWidth="true"/>
-    <col min="15" max="15" width="10.0" customWidth="true"/>
-    <col min="16" max="16" width="14.0" customWidth="true"/>
-    <col min="17" max="17" width="14.0" customWidth="true"/>
-    <col min="18" max="18" width="14.0" customWidth="true"/>
-    <col min="19" max="19" width="12.0" customWidth="true"/>
+    <col min="14" max="14" width="18.0" customWidth="true"/>
+    <col min="15" max="15" width="16.0" customWidth="true"/>
+    <col min="16" max="16" width="22.0" customWidth="true"/>
+    <col min="17" max="17" width="8.0" customWidth="true"/>
+    <col min="18" max="18" width="12.0" customWidth="true"/>
+    <col min="19" max="19" width="10.0" customWidth="true"/>
+    <col min="20" max="20" width="12.0" customWidth="true"/>
+    <col min="21" max="21" width="10.0" customWidth="true"/>
+    <col min="22" max="22" width="14.0" customWidth="true"/>
+    <col min="23" max="23" width="14.0" customWidth="true"/>
+    <col min="24" max="24" width="14.0" customWidth="true"/>
+    <col min="25" max="25" width="12.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -243,6 +267,24 @@
       </c>
       <c r="S2" t="s" s="2">
         <v>19</v>
+      </c>
+      <c r="T2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U2" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V2" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W2" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X2" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="Y2" t="s" s="2">
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -265,6 +307,12 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
